--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487666_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487666_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. ARMSTRONG</t>
+          <t>B. OJEDA OCHOA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.4041</v>
+        <v>6.7063</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0898</v>
+        <v>8.0099</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3143</v>
+        <v>-1.3036</v>
       </c>
       <c r="G2" t="n">
-        <v>6.6945</v>
+        <v>5.1053</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.2564</v>
+        <v>0.9466</v>
       </c>
       <c r="I2" t="n">
-        <v>7.9509</v>
+        <v>4.1587</v>
       </c>
       <c r="J2" t="n">
-        <v>7.5752</v>
+        <v>7.2151</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.5314</v>
+        <v>1.4047</v>
       </c>
       <c r="L2" t="n">
-        <v>8.1066</v>
+        <v>5.8104</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.8808</v>
+        <v>-2.1098</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.725</v>
+        <v>-0.4581</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1557</v>
+        <v>-1.6517</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.1642</v>
+        <v>0.9702</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R2" t="n">
-        <v>0.7761</v>
+        <v>1.9403</v>
       </c>
       <c r="S2" t="n">
-        <v>0.544</v>
+        <v>0.6309</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5451</v>
+        <v>0.5411</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0891</v>
+        <v>0.0897</v>
       </c>
       <c r="V2" t="n">
-        <v>0.3299</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3299</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. OJEDA OCHOA</t>
+          <t>A. ARMSTRONG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.8332</v>
+        <v>6.5597</v>
       </c>
       <c r="E3" t="n">
-        <v>7.4093</v>
+        <v>5.7905</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.5762</v>
+        <v>0.7692</v>
       </c>
       <c r="G3" t="n">
-        <v>5.1053</v>
+        <v>6.6945</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9466</v>
+        <v>-1.2564</v>
       </c>
       <c r="I3" t="n">
-        <v>4.1587</v>
+        <v>7.9509</v>
       </c>
       <c r="J3" t="n">
-        <v>7.2151</v>
+        <v>7.5752</v>
       </c>
       <c r="K3" t="n">
-        <v>1.4047</v>
+        <v>-0.5314</v>
       </c>
       <c r="L3" t="n">
-        <v>5.8104</v>
+        <v>8.1066</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.1098</v>
+        <v>-0.8808</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4581</v>
+        <v>-0.725</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.6517</v>
+        <v>-0.1557</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9702</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9403</v>
+        <v>0.7761</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2423</v>
+        <v>0.6996</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0595</v>
+        <v>0.1556</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1828</v>
+        <v>0.544</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.3299</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2239</v>
+        <v>0.3299</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5338</v>
+        <v>4.6611</v>
       </c>
       <c r="E4" t="n">
-        <v>3.936</v>
+        <v>4.0361</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5978</v>
+        <v>0.625</v>
       </c>
       <c r="G4" t="n">
         <v>2.794</v>
@@ -766,13 +766,13 @@
         <v>1.3582</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3816</v>
+        <v>0.5089</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1222</v>
+        <v>0.2223</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2593</v>
+        <v>0.2866</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.8206</v>
+        <v>3.2106</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3613</v>
+        <v>1.5605</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4593</v>
+        <v>1.6501</v>
       </c>
       <c r="G5" t="n">
         <v>1.3719</v>
@@ -844,13 +844,13 @@
         <v>1.9403</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0861</v>
+        <v>0.4761</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1541</v>
+        <v>0.3533</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0679</v>
+        <v>0.1228</v>
       </c>
       <c r="V5" t="n">
         <v>1.3626</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. BUSTOS NGUEMA</t>
+          <t>M. DIALLO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.256</v>
+        <v>2.0572</v>
       </c>
       <c r="E6" t="n">
-        <v>3.6404</v>
+        <v>1.6928</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3844</v>
+        <v>0.3644</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0039</v>
+        <v>2.2539</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.754</v>
+        <v>1.2902</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7579</v>
+        <v>0.9637</v>
       </c>
       <c r="J6" t="n">
-        <v>1.34</v>
+        <v>1.8494</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.38</v>
+        <v>0.9969</v>
       </c>
       <c r="L6" t="n">
-        <v>2.72</v>
+        <v>0.8525</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3362</v>
+        <v>0.4045</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.374</v>
+        <v>0.2933</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9621</v>
+        <v>0.1112</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1642</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R6" t="n">
         <v>1.1642</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6193</v>
+        <v>1.1914</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6079</v>
+        <v>0.8897</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0115</v>
+        <v>0.3017</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4686</v>
+        <v>-0.6119</v>
       </c>
       <c r="W6" t="n">
-        <v>1.6925</v>
+        <v>0.894</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2239</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. DIAZ ZARZUELA</t>
+          <t>J. BUSTOS NGUEMA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.0924</v>
+        <v>2.0191</v>
       </c>
       <c r="E7" t="n">
-        <v>2.6409</v>
+        <v>3.24</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5485</v>
+        <v>-1.2209</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3391</v>
+        <v>0.0039</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4721</v>
+        <v>-1.754</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1329</v>
+        <v>1.7579</v>
       </c>
       <c r="J7" t="n">
-        <v>2.2147</v>
+        <v>1.34</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7127</v>
+        <v>-1.38</v>
       </c>
       <c r="L7" t="n">
-        <v>1.5021</v>
+        <v>2.72</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.8756</v>
+        <v>-1.3362</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2406</v>
+        <v>-0.374</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.635</v>
+        <v>-0.9621</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5821</v>
+        <v>1.1642</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5523</v>
+        <v>1.1642</v>
       </c>
       <c r="S7" t="n">
-        <v>2.395</v>
+        <v>0.3824</v>
       </c>
       <c r="T7" t="n">
-        <v>1.3963</v>
+        <v>0.2075</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9987</v>
+        <v>0.175</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2239</v>
+        <v>0.4686</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.6925</v>
       </c>
       <c r="X7" t="n">
         <v>-1.2239</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. DIALLO</t>
+          <t>F. DIAZ ZARZUELA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7391</v>
+        <v>0.4645</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5927</v>
+        <v>1.6399</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1464</v>
+        <v>-1.1754</v>
       </c>
       <c r="G8" t="n">
-        <v>2.2539</v>
+        <v>0.3391</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2902</v>
+        <v>0.4721</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9637</v>
+        <v>-0.1329</v>
       </c>
       <c r="J8" t="n">
-        <v>1.8494</v>
+        <v>2.2147</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9969</v>
+        <v>0.7127</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8525</v>
+        <v>1.5021</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4045</v>
+        <v>-1.8756</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2933</v>
+        <v>-0.2406</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1112</v>
+        <v>-1.635</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7761</v>
+        <v>0.5821</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1642</v>
+        <v>1.5523</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8733</v>
+        <v>0.7672</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7896</v>
+        <v>0.3953</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0837</v>
+        <v>0.3718</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6119</v>
+        <v>-1.2239</v>
       </c>
       <c r="W8" t="n">
-        <v>0.894</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.506</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9181</v>
+        <v>-1.7635</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0189</v>
+        <v>-0.9188</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8992</v>
+        <v>-0.8447</v>
       </c>
       <c r="G10" t="n">
         <v>-2.3434</v>
@@ -1234,13 +1234,13 @@
         <v>1.3582</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2909</v>
+        <v>0.4455</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1828</v>
+        <v>0.2829</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1081</v>
+        <v>0.1626</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2239</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.11</v>
+        <v>-3.2642</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.8411</v>
+        <v>-2.2405</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2689</v>
+        <v>-1.0236</v>
       </c>
       <c r="G11" t="n">
         <v>-3.1349</v>
@@ -1312,13 +1312,13 @@
         <v>1.1642</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9154</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8479</v>
+        <v>-0.2473</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0675</v>
+        <v>0.1778</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2239</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>20.4575</v>
+        <v>20.4572</v>
       </c>
       <c r="E12" t="n">
-        <v>22.6287</v>
+        <v>22.62869999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.1713</v>
+        <v>-2.1714</v>
       </c>
       <c r="G12" t="n">
         <v>12.8783</v>
@@ -1396,7 +1396,7 @@
         <v>2.6187</v>
       </c>
       <c r="U12" t="n">
-        <v>2.2322</v>
+        <v>2.232</v>
       </c>
       <c r="V12" t="n">
         <v>-2.1225</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.519</v>
+        <v>3.7375</v>
       </c>
       <c r="E13" t="n">
-        <v>3.0203</v>
+        <v>3.3206</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4987</v>
+        <v>0.4169</v>
       </c>
       <c r="G13" t="n">
         <v>2.1604</v>
@@ -1468,13 +1468,13 @@
         <v>0.5821</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.225</v>
+        <v>-0.0064</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5451</v>
+        <v>-0.2448</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3201</v>
+        <v>0.2384</v>
       </c>
       <c r="V13" t="n">
         <v>2.1657</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. BARCALA BELTRAN</t>
+          <t>D. ROPERO MORA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1475</v>
+        <v>-0.1684</v>
       </c>
       <c r="E14" t="n">
-        <v>3.8164</v>
+        <v>0.1821</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.6689</v>
+        <v>-0.3505</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3586</v>
+        <v>-0.2104</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3254</v>
+        <v>0.0387</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6840000000000001</v>
+        <v>-0.2492</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1366</v>
+        <v>0.2242</v>
       </c>
       <c r="K14" t="n">
-        <v>1.2235</v>
+        <v>0.0618</v>
       </c>
       <c r="L14" t="n">
-        <v>1.9131</v>
+        <v>0.1624</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.7779</v>
+        <v>-0.4346</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.5489</v>
+        <v>-0.0231</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.229</v>
+        <v>-0.4115</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>0.194</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9702</v>
+        <v>0.194</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2111</v>
+        <v>0.1301</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4262</v>
+        <v>-0.0421</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6373</v>
+        <v>0.1722</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2239</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. ROPERO MORA</t>
+          <t>P. BARCALA BELTRAN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.4503</v>
+        <v>-0.2078</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0181</v>
+        <v>3.2158</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4323</v>
+        <v>-3.4236</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2104</v>
+        <v>0.3586</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0387</v>
+        <v>-0.3254</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2492</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2242</v>
+        <v>3.1366</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0618</v>
+        <v>1.2235</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1624</v>
+        <v>1.9131</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4346</v>
+        <v>-2.7779</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0231</v>
+        <v>-1.5489</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4115</v>
+        <v>-1.229</v>
       </c>
       <c r="P15" t="n">
-        <v>0.194</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R15" t="n">
-        <v>0.194</v>
+        <v>0.9702</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1519</v>
+        <v>-0.5664</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2423</v>
+        <v>-0.1744</v>
       </c>
       <c r="U15" t="n">
-        <v>0.09039999999999999</v>
+        <v>-0.392</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2821</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.6647</v>
+        <v>-1.9011</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2215</v>
+        <v>1.1214</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.8862</v>
+        <v>-3.0225</v>
       </c>
       <c r="G16" t="n">
         <v>-1.5464</v>
@@ -1702,13 +1702,13 @@
         <v>0.9702</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6124000000000001</v>
+        <v>-0.8488</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0595</v>
+        <v>-0.1596</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5528999999999999</v>
+        <v>-0.6892</v>
       </c>
       <c r="V16" t="n">
         <v>-0.2821</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.8514</v>
+        <v>-2.0338</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3258</v>
+        <v>-0.0746</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.1773</v>
+        <v>-1.9592</v>
       </c>
       <c r="G17" t="n">
         <v>-1.1146</v>
@@ -1780,13 +1780,13 @@
         <v>0.3881</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.08459999999999999</v>
+        <v>-0.2669</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3039</v>
+        <v>-0.0965</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3885</v>
+        <v>-0.1705</v>
       </c>
       <c r="V17" t="n">
         <v>-0.8462</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.1127</v>
+        <v>-3.3396</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.5674</v>
+        <v>-2.0669</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5452</v>
+        <v>-1.2727</v>
       </c>
       <c r="G18" t="n">
         <v>-1.3559</v>
@@ -1858,13 +1858,13 @@
         <v>0.7761</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9702</v>
+        <v>-0.1971</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7874</v>
+        <v>-0.2869</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1828</v>
+        <v>0.0897</v>
       </c>
       <c r="V18" t="n">
         <v>-0.2343</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. GARCIA GALLARDO</t>
+          <t>F. ESPINOSA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.5477</v>
+        <v>-5.2437</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5608</v>
+        <v>0.3152</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.9869</v>
+        <v>-5.5589</v>
       </c>
       <c r="G19" t="n">
-        <v>-5.3703</v>
+        <v>-3.1777</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.6766</v>
+        <v>-0.0379</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.6938</v>
+        <v>-3.1398</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.6307</v>
+        <v>1.0524</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.2069</v>
+        <v>1.1946</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.4237</v>
+        <v>-0.1422</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.7397</v>
+        <v>-4.2301</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4696</v>
+        <v>-1.2325</v>
       </c>
       <c r="O19" t="n">
-        <v>-3.27</v>
+        <v>-2.9975</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7761</v>
+        <v>-1.7463</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.3881</v>
+        <v>-3.1045</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1642</v>
+        <v>1.3582</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9405</v>
+        <v>-0.9794</v>
       </c>
       <c r="T19" t="n">
-        <v>1.458</v>
+        <v>-0.6923</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5175</v>
+        <v>-0.2871</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.894</v>
+        <v>0.6597</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>3.0597</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.894</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. ESPINOSA</t>
+          <t>P. VILLANUEVA LAZARO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.5628</v>
+        <v>-5.2608</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3855</v>
+        <v>-1.3684</v>
       </c>
       <c r="F20" t="n">
-        <v>-5.1773</v>
+        <v>-3.8924</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.1777</v>
+        <v>-2.6218</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0379</v>
+        <v>-0.6904</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.1398</v>
+        <v>-1.9314</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0524</v>
+        <v>1.4748</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1946</v>
+        <v>0.6756</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.1422</v>
+        <v>0.7992</v>
       </c>
       <c r="M20" t="n">
-        <v>-4.2301</v>
+        <v>-4.0966</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2325</v>
+        <v>-1.366</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.9975</v>
+        <v>-2.7306</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.7463</v>
+        <v>-2.9105</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.1045</v>
+        <v>-4.2687</v>
       </c>
       <c r="R20" t="n">
         <v>1.3582</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2985</v>
+        <v>-1.5643</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.393</v>
+        <v>-0.6923</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0945</v>
+        <v>-0.872</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6597</v>
+        <v>1.8358</v>
       </c>
       <c r="W20" t="n">
-        <v>3.0597</v>
+        <v>2.1179</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.4</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. VILLANUEVA LAZARO</t>
+          <t>I. GARCIA GALLARDO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.9342</v>
+        <v>-6.0398</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0691</v>
+        <v>-1.8621</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.8652</v>
+        <v>-4.1777</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.6218</v>
+        <v>-5.3703</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6904</v>
+        <v>-1.6766</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.9314</v>
+        <v>-3.6938</v>
       </c>
       <c r="J21" t="n">
-        <v>1.4748</v>
+        <v>-1.6307</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6756</v>
+        <v>-1.2069</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7992</v>
+        <v>-0.4237</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.0966</v>
+        <v>-3.7397</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.366</v>
+        <v>-0.4696</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.7306</v>
+        <v>-3.27</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.9105</v>
+        <v>0.7761</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.2687</v>
+        <v>-0.3881</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3582</v>
+        <v>1.1642</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.2378</v>
+        <v>-0.5515</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.393</v>
+        <v>0.1567</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8447</v>
+        <v>-0.7082000000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>1.8358</v>
+        <v>-0.894</v>
       </c>
       <c r="W21" t="n">
-        <v>2.1179</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2821</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="22">
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-20.4573</v>
+        <v>-20.4575</v>
       </c>
       <c r="E22" t="n">
-        <v>2.783100000000001</v>
+        <v>2.7831</v>
       </c>
       <c r="F22" t="n">
         <v>-23.2406</v>
@@ -2143,25 +2143,25 @@
         <v>-10.0936</v>
       </c>
       <c r="J22" t="n">
-        <v>9.7201</v>
+        <v>9.720099999999999</v>
       </c>
       <c r="K22" t="n">
         <v>2.7685</v>
       </c>
       <c r="L22" t="n">
-        <v>6.951999999999999</v>
+        <v>6.952</v>
       </c>
       <c r="M22" t="n">
         <v>-22.5984</v>
       </c>
       <c r="N22" t="n">
-        <v>-5.552999999999999</v>
+        <v>-5.553</v>
       </c>
       <c r="O22" t="n">
         <v>-17.0451</v>
       </c>
       <c r="P22" t="n">
-        <v>-4.851</v>
+        <v>-4.850999999999999</v>
       </c>
       <c r="Q22" t="n">
         <v>-12.6121</v>
@@ -2170,7 +2170,7 @@
         <v>7.7613</v>
       </c>
       <c r="S22" t="n">
-        <v>-4.851</v>
+        <v>-4.850700000000001</v>
       </c>
       <c r="T22" t="n">
         <v>-2.2322</v>
@@ -2182,7 +2182,7 @@
         <v>2.1225</v>
       </c>
       <c r="W22" t="n">
-        <v>7.907500000000001</v>
+        <v>7.9075</v>
       </c>
       <c r="X22" t="n">
         <v>-5.785</v>
